--- a/docs/test-cases/SPM-64_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-64_Test_Cases.xlsx
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM64 Closed Registration Seminar (Confirmed, starts 10 Mar 2027, 09:00) | Closes: 30 Sep 2026, 17:00 (already past) -&gt; 28 Feb 2027, 17:00</t>
+          <t>Event: SPM64 Closed Registration Seminar (Confirmed, starts 10 Mar 2027, 09:00) | Closes: 30 Sept 2026, 17:00 (already past) -&gt; 28 Feb 2027, 17:00</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 1: The card shows 'Closes: 30 Sep 2026, 17:00', a date that has already passed.
+          <t>Step 1: The card shows 'Closes: 30 Sept 2026, 17:00', a date that has already passed.
 Step 4: 'Registration settings saved.' appears. The card shows 'Opens: 1 Aug 2026, 09:00' and 'Closes: 28 Feb 2027, 17:00'. The status badge still reads 'Confirmed'.</t>
         </is>
       </c>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Events: SPM64 Twin Room Workshop (registration off), SPM64 Closed Registration Seminar (on, capacity 50, 1 Aug 2026 09:00 – 30 Sep 2026 17:00) | Organiser: Evelyn Chen | Colleague: Raj Kumar (Straits Medical Institute)</t>
+          <t>Events: SPM64 Twin Room Workshop (registration off), SPM64 Closed Registration Seminar (on, capacity 50, 1 Aug 2026 09:00 – 30 Sept 2026 17:00) | Organiser: Evelyn Chen | Colleague: Raj Kumar (Straits Medical Institute)</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and no 'Change registration settings' button.
-Step 2: The card shows 'Registration: Enabled', 'Capacity: 50', 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sep 2026, 17:00', with no 'Change registration settings' button.
+Step 2: The card shows 'Registration: Enabled', 'Capacity: 50', 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00', with no 'Change registration settings' button.
 Step 4: The same values as in step 2, with no 'Change registration settings' button.</t>
         </is>
       </c>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM64 Closed Registration Seminar (Confirmed, no registrations) | Capacity 50 | Opens 1 Aug 2026, 09:00 | Closes 30 Sep 2026, 17:00</t>
+          <t>Event: SPM64 Closed Registration Seminar (Confirmed, no registrations) | Capacity 50 | Opens 1 Aug 2026, 09:00 | Closes 30 Sept 2026, 17:00</t>
         </is>
       </c>
     </row>
@@ -4714,9 +4714,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 1: The card shows 'Registration: Enabled', 'Capacity: 50', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sep 2026, 17:00'.
+          <t>Step 1: The card shows 'Registration: Enabled', 'Capacity: 50', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00'.
 Step 4: 'Registration settings saved.' appears, the card shows 'Registration: Not enabled for this event', and no 'Flagged for review' list is shown (nobody holds a place). The status badge still reads 'Confirmed'.
-Step 6: 'Registration capacity' shows 50, 'Registration opens' 1 Aug 2026 09:00 and 'Registration closes' 30 Sep 2026 17:00.
+Step 6: 'Registration capacity' shows 50, 'Registration opens' 1 Aug 2026 09:00 and 'Registration closes' 30 Sept 2026 17:00.
 Step 7: The card shows 'Registration: Enabled', 'Capacity: 50' and the same opening and closing times as in step 1.</t>
         </is>
       </c>

--- a/docs/test-cases/SPM-64_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-64_Test_Cases.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1586,8 +1586,33 @@
       </c>
       <c r="F42" s="9" t="n"/>
     </row>
+    <row r="44" ht="139" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Code reviewed</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>src/app/api/events/[id]/registration/route.ts
+src/lib/registrationSettings.ts
+src/lib/eventConfirmation.ts
+src/lib/permissions.ts
+src/lib/validation/registrations.ts
+src/app/events/[id]/RegistrationCard.tsx
+src/app/events/[id]/page.tsx
+src/app/api/events/[id]/route.ts
+prisma/schema.prisma
+scripts/seed-spm64.ts</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E42:F42"/>
@@ -1603,6 +1628,7 @@
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
@@ -1720,7 +1746,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM64 Twin Room Workshop | Bookings: Orchard Seminar Room Classroom 70 (Approved), Orchard Studio Classroom 40 (Pending), Marina Bay Ballroom (Rejected) | Chosen: Orchard Studio | Capacity: 45, then 40</t>
+          <t>Event: SPM64 Twin Room Workshop | Bookings: Orchard Seminar Room Classroom 70 (Approved), Orchard Studio Classroom 40 (Pending), Marina Grand Hall (Rejected) | Chosen: Orchard Studio | Capacity: 45, then 40</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1759,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' and 'Capacity measured against' appear. The list is set to 'Choose a booking'.
-Step 4: The list offers exactly two bookings: 'Orchard Seminar Room (ORC-SEM) · Classroom · up to 70 · Approved' and 'Orchard Studio (ORC-STU) · Classroom · up to 40 · Pending'. The rejected Marina Bay Ballroom booking is not offered.
+Step 4: The list offers exactly two bookings: 'Orchard Seminar Room (ORC-SEM) · Classroom · up to 70 · Approved' and 'Orchard Studio (ORC-STU) · Classroom · up to 40 · Pending'. The rejected Marina Grand Hall booking is not offered.
 Step 7: 'Registration capacity can't be more than 40, the capacity of Orchard Studio (ORC-STU) in its Classroom layout.' shows under 'Registration capacity', and nothing is saved.
 Step 9: 'Registration settings saved.' appears. The card shows 'Capacity: 40' and 'Measured against: Orchard Studio (ORC-STU), Classroom layout – up to 40'.</t>
         </is>
@@ -2050,7 +2076,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM64 Orchard Data Forum (17 Mar 2027, 09:00–17:00) | Opens: 1 Feb 2027, 09:00 | Closes: 10 Mar 2027, 17:00</t>
+          <t>Event: SPM64 Orchard Data Forum (18 Mar 2027, 09:00–17:00) | Opens: 1 Feb 2027, 09:00 | Closes: 10 Mar 2027, 17:00</t>
         </is>
       </c>
     </row>
@@ -2062,8 +2088,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 1: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00'.
-Step 6: 'Registration settings saved.' appears. The card shows 'Opens: 1 Feb 2027, 09:00' and 'Closes: 10 Mar 2027, 17:00'. 'When' in the Details card still shows '17 Mar 2027, 09:00–17:00'.</t>
+          <t>Step 1: 'When' in the Details card shows '18 Mar 2027, 09:00–17:00'.
+Step 6: 'Registration settings saved.' appears. The card shows 'Opens: 1 Feb 2027, 09:00' and 'Closes: 10 Mar 2027, 17:00'. 'When' in the Details card still shows '18 Mar 2027, 09:00–17:00'.</t>
         </is>
       </c>
     </row>
@@ -2369,9 +2395,9 @@
 2. Click 'Change registration settings' on the Registration card
 3. Tick 'Attendees need to register for this event'
 4. Enter 1 Feb 2027, 09:00 in 'Registration opens'
-5. Enter 17 Mar 2027, 09:01 in 'Registration closes'
+5. Enter 18 Mar 2027, 09:01 in 'Registration closes'
 6. Click 'Save registration settings'
-7. Change 'Registration closes' to 17 Mar 2027, 09:00
+7. Change 'Registration closes' to 18 Mar 2027, 09:00
 8. Click 'Save registration settings'</t>
         </is>
       </c>
@@ -2384,7 +2410,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM64 Orchard Data Forum (starts 17 Mar 2027, 09:00) | Opens: 1 Feb 2027, 09:00 | Closes: 17 Mar 2027, 09:01, then 09:00</t>
+          <t>Event: SPM64 Orchard Data Forum (starts 18 Mar 2027, 09:00) | Opens: 1 Feb 2027, 09:00 | Closes: 18 Mar 2027, 09:01, then 09:00</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2423,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Step 6: 'Registration must close no later than the event starts.' shows under 'Registration closes', and nothing is saved.
-Step 8: 'Registration settings saved.' appears, and the card shows 'Closes: 17 Mar 2027, 09:00'.</t>
+Step 8: 'Registration settings saved.' appears, and the card shows 'Closes: 18 Mar 2027, 09:00'.</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3411,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="166" customHeight="1">
+    <row r="6" ht="206.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3396,7 +3422,7 @@
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and a 'Change registration settings' button.
 Step 2: The card shows the checkbox 'Attendees need to register for this event', not ticked, and the buttons 'Save registration settings' and 'Cancel'.
 Step 3: 'Registration capacity', 'Registration opens' and 'Registration closes' appear, empty.
-Step 4: A green alert 'Registration settings saved.' appears. The card shows 'Registration: Enabled', 'Capacity: —', 'Opens: —' and 'Closes: —'.
+Step 4: A green alert 'Registration settings saved.' appears. The card shows 'Registration: Enabled', 'Capacity: —', 'Measured against: —', 'Opens: —' and 'Closes: —', and an amber alert 'Registration setup is incomplete' reads 'Still needed: registration capacity, opening date, closing date.' (checked in SPM-64-TC16).
 Step 5: The card still shows 'Registration: Enabled'.</t>
         </is>
       </c>

--- a/docs/test-cases/SPM-64_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-64_Test_Cases.xlsx
@@ -40,7 +40,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -64,6 +64,9 @@
       <color rgb="FF1155CC"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -149,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -199,6 +202,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,12 +497,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="19">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>SPM-64: As the assigned Event Coordinator, I want to set up attendee registration for an event so that Attendees can register only when, and in the numbers, the event allows</t>
         </is>
@@ -508,32 +514,32 @@
     </row>
     <row r="2" ht="12" customHeight="1" s="19"/>
     <row r="3" ht="12.75" customHeight="1" s="19">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -560,27 +566,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>The assigned coordinator turns registration on</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -599,27 +605,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC02</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Turning registration off keeps its saved settings for when it is turned back on</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -638,27 +644,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC03</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Registration settings can't be changed on a Postponed event</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -677,27 +683,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC04</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Setting a capacity on an event with one booking measures it against that booking automatically</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>AC2, AC4</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -716,27 +722,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC05</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>A capacity that isn't a whole number of at least 1 is refused</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -755,27 +761,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC06</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>The capacity can equal the room's capacity for the booked layout, but not exceed it</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -794,27 +800,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC07</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>A capacity can't be set before the event has a venue booking</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -833,27 +839,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC08</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>A capacity can't be set when the booking has no room layout</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -872,27 +878,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC09</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>With two bookings the coordinator chooses which one the capacity is measured against</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -911,27 +917,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC10</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>With two bookings a capacity can't be saved until a booking is chosen</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -950,27 +956,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC11</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>The registration period is set separately from the event's own date</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -989,27 +995,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC12</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Registration can't close before, or at the same moment as, it opens</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1028,27 +1034,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC13</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Registration can close exactly when the event starts, but not after</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1067,27 +1073,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC14</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>A registration period that has closed is reopened by moving its closing date later</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1106,27 +1112,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC15</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>The registration period can't be changed once the event has started</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1145,27 +1151,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC16</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Incomplete registration setup is outstanding and blocks confirmation until every setting is in place</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1188,27 +1194,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC17</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Registration that is turned off is not an outstanding arrangement</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1231,27 +1237,27 @@
           <t>TC18</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC18</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>A capacity measured against a booking that is no longer active is outstanding until another booking is chosen</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>AC8, AC4</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1274,27 +1280,27 @@
           <t>TC19</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC19</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Lowering the capacity below the attendees holding a place saves it and flags the registrations</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1313,27 +1319,27 @@
           <t>TC20</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC20</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Lowering the capacity to exactly the attendees holding a place flags nothing</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1352,27 +1358,27 @@
           <t>TC21</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC21</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>Turning registration off with only waitlisted attendees saves it and flags the registrations</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1391,27 +1397,27 @@
           <t>TC22</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC22</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>A registered attendee still sees the event after registration is turned off, and a withdrawn one doesn't</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1430,27 +1436,27 @@
           <t>TC23</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC23</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>The organiser and a colleague from their company see the settings but can't change them</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>AC10</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1469,38 +1475,42 @@
           <t>TC24</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC24</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>Staff other than the assigned coordinator can't change registration settings</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H27" s="23" t="n"/>
-      <c r="I27" s="23" t="n"/>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24.75" customHeight="1" s="19">
       <c r="A28" s="15" t="inlineStr">
@@ -1508,27 +1518,27 @@
           <t>TC25</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC25</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>An attendee sees an open event's registration details but can't change them</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1544,19 +1554,19 @@
     <row r="29" ht="12" customHeight="1" s="19"/>
     <row r="30" ht="12" customHeight="1" s="19"/>
     <row r="31" ht="12.75" customHeight="1" s="19">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="21" t="n"/>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1564,19 +1574,19 @@
       <c r="F31" s="21" t="n"/>
     </row>
     <row r="32" ht="44.25" customHeight="1" s="19">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>The assigned Event Coordinator can enable or disable attendee registration for an event.</t>
         </is>
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="21" t="n"/>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC01
 SPM-64-TC02
@@ -1586,19 +1596,19 @@
       <c r="F32" s="21" t="n"/>
     </row>
     <row r="33" ht="30.75" customHeight="1" s="19">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>The Coordinator can set a registration capacity for the event.</t>
         </is>
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="21" t="n"/>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC04
 SPM-64-TC05</t>
@@ -1607,19 +1617,19 @@
       <c r="F33" s="21" t="n"/>
     </row>
     <row r="34" ht="44.25" customHeight="1" s="19">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>The registration capacity cannot exceed the capacity of the event's booked venue for its selected room layout.</t>
         </is>
       </c>
       <c r="C34" s="20" t="n"/>
       <c r="D34" s="21" t="n"/>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC06
 SPM-64-TC07
@@ -1629,19 +1639,19 @@
       <c r="F34" s="21" t="n"/>
     </row>
     <row r="35" ht="57.75" customHeight="1" s="19">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Given the event has more than one venue booking, when the Coordinator sets the registration capacity, then they select which venue booking the capacity is measured against, and the capacity cannot exceed that venue's capacity for its selected layout (see SPM-81).</t>
         </is>
       </c>
       <c r="C35" s="20" t="n"/>
       <c r="D35" s="21" t="n"/>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC04
 SPM-64-TC09
@@ -1652,19 +1662,19 @@
       <c r="F35" s="21" t="n"/>
     </row>
     <row r="36" ht="30.75" customHeight="1" s="19">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>The Coordinator can set a registration opening date and closing date that are separate from the event date.</t>
         </is>
       </c>
       <c r="C36" s="20" t="n"/>
       <c r="D36" s="21" t="n"/>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC11</t>
         </is>
@@ -1672,19 +1682,19 @@
       <c r="F36" s="21" t="n"/>
     </row>
     <row r="37" ht="30.75" customHeight="1" s="19">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>The closing date cannot be earlier than the opening date or later than the event's start.</t>
         </is>
       </c>
       <c r="C37" s="20" t="n"/>
       <c r="D37" s="21" t="n"/>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC12
 SPM-64-TC13</t>
@@ -1693,19 +1703,19 @@
       <c r="F37" s="21" t="n"/>
     </row>
     <row r="38" ht="30.75" customHeight="1" s="19">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>The Coordinator can extend or reopen a closed registration period, provided the event has not started.</t>
         </is>
       </c>
       <c r="C38" s="20" t="n"/>
       <c r="D38" s="21" t="n"/>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC14
 SPM-64-TC15</t>
@@ -1714,19 +1724,19 @@
       <c r="F38" s="21" t="n"/>
     </row>
     <row r="39" ht="57.75" customHeight="1" s="19">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>Given registration is enabled, when the settings are incomplete (no capacity or no registration period), then the event's registration setup is shown as an outstanding arrangement (see Track Outstanding Arrangements).</t>
         </is>
       </c>
       <c r="C39" s="20" t="n"/>
       <c r="D39" s="21" t="n"/>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC16
 SPM-64-TC17
@@ -1736,19 +1746,19 @@
       <c r="F39" s="21" t="n"/>
     </row>
     <row r="40" ht="57.75" customHeight="1" s="19">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>Given Attendees are registered or on the waiting list, when the Coordinator lowers the registration capacity below that number or disables registration, then the change is saved and the event's registrations are flagged for review rather than changed (see SPM-68).</t>
         </is>
       </c>
       <c r="C40" s="20" t="n"/>
       <c r="D40" s="21" t="n"/>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC19
 SPM-64-TC20
@@ -1759,19 +1769,19 @@
       <c r="F40" s="21" t="n"/>
     </row>
     <row r="41" ht="30.75" customHeight="1" s="19">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>AC10</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>The Event Organiser can view the registration settings for their event but cannot change them.</t>
         </is>
       </c>
       <c r="C41" s="20" t="n"/>
       <c r="D41" s="21" t="n"/>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC23</t>
         </is>
@@ -1779,19 +1789,19 @@
       <c r="F41" s="21" t="n"/>
     </row>
     <row r="42" ht="30.75" customHeight="1" s="19">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>AC11</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>Users other than the assigned Coordinator cannot change registration settings.</t>
         </is>
       </c>
       <c r="C42" s="20" t="n"/>
       <c r="D42" s="21" t="n"/>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC24
 SPM-64-TC25</t>
@@ -1801,12 +1811,12 @@
     </row>
     <row r="43" ht="12" customHeight="1" s="19"/>
     <row r="44" ht="138.75" customHeight="1" s="19">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>src/app/api/events/[id]/registration/route.ts
 src/lib/registrationSettings.ts
@@ -2870,7 +2880,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC09</t>
         </is>
@@ -2882,7 +2892,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -2896,7 +2906,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Twin Room Workshop'
 2. Click 'Change registration settings' on the Registration card
@@ -2916,7 +2926,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Twin Room Workshop | Bookings: Orchard Seminar Room Classroom 70 (Approved), Orchard Studio Classroom 40 (Pending), Marina Grand Hall (Rejected) | Chosen: Orchard Studio | Capacity: 45, then 40</t>
         </is>
@@ -2928,7 +2938,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' and 'Capacity measured against' appear. The list is set to 'Choose a booking'.
 Step 4: The list offers exactly two bookings: 'Orchard Seminar Room (ORC-SEM) · Classroom · up to 70 · Approved' and 'Orchard Studio (ORC-STU) · Classroom · up to 40 · Pending'. The rejected Marina Grand Hall booking is not offered.
@@ -2943,7 +2953,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -2975,7 +2985,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' and 'Capacity measured against' appear. The list is set to 'Choose a booking'.
 Step 4: The list offers exactly two bookings: 'Orchard Seminar Room (ORC-SEM) · Classroom · up to 70 · Approved' and 'Orchard Studio (ORC-STU) · Classroom · up to 40 · Pending'. The rejected Marina Grand Hall booking is not offered.
@@ -3045,7 +3055,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' and 'Capacity measured against' appear. The list is set to 'Choose a booking'.
 Step 4: The list offers exactly two bookings: 'Orchard Seminar Room (ORC-SEM) · Classroom · up to 70 · Approved' and 'Orchard Studio (ORC-STU) · Classroom · up to 40 · Pending'. The rejected Marina Grand Hall booking is not offered.
@@ -4112,7 +4122,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC10</t>
         </is>
@@ -4124,7 +4134,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -4138,7 +4148,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Twin Room Workshop'
 2. Click 'Change registration settings' on the Registration card
@@ -4154,7 +4164,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Twin Room Workshop (two live bookings) | Capacity: 30 | 'Capacity measured against' left at 'Choose a booking'</t>
         </is>
@@ -4166,7 +4176,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Choose which venue booking the capacity is measured against.' shows under 'Capacity measured against'. The form stays open and nothing is saved.</t>
         </is>
@@ -4178,7 +4188,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -4210,7 +4220,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Choose which venue booking the capacity is measured against.' shows under 'Capacity measured against'. The form stays open and nothing is saved.</t>
         </is>
@@ -4277,7 +4287,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Choose which venue booking the capacity is measured against.' shows under 'Capacity measured against'. The form stays open and nothing is saved.</t>
         </is>
@@ -5341,7 +5351,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC11</t>
         </is>
@@ -5353,7 +5363,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -5367,7 +5377,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -5384,7 +5394,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum (18 Mar 2027, 09:00–17:00) | Opens: 1 Feb 2027, 09:00 | Closes: 10 Mar 2027, 17:00</t>
         </is>
@@ -5396,7 +5406,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: 'When' in the Details card shows '18 Mar 2027, 09:00–17:00'.
 Step 6: 'Registration settings saved.' appears. The card shows 'Opens: 1 Feb 2027, 09:00' and 'Closes: 10 Mar 2027, 17:00'. 'When' in the Details card still shows '18 Mar 2027, 09:00–17:00'.</t>
@@ -5409,7 +5419,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -5441,7 +5451,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: 'When' in the Details card shows '18 Mar 2027, 09:00–17:00'.
 Step 6: 'Registration settings saved.' appears. The card shows 'Opens: 1 Feb 2027, 09:00' and 'Closes: 10 Mar 2027, 17:00'. 'When' in the Details card still shows '18 Mar 2027, 09:00–17:00'.</t>
@@ -5509,7 +5519,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: 'When' in the Details card shows '18 Mar 2027, 09:00–17:00'.
 Step 6: 'Registration settings saved.' appears. The card shows 'Opens: 1 Feb 2027, 09:00' and 'Closes: 10 Mar 2027, 17:00'. 'When' in the Details card still shows '18 Mar 2027, 09:00–17:00'.</t>
@@ -6574,7 +6584,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC12</t>
         </is>
@@ -6586,7 +6596,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -6600,7 +6610,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -6619,7 +6629,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum | Opens: 1 Mar 2027, 09:00 | Closes: 1 Feb 2027, 09:00, then 1 Mar 2027, 09:00</t>
         </is>
@@ -6631,7 +6641,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 6: 'Registration closes at must be after it opens.' shows under 'Registration closes', and nothing is saved.
 Step 8: The same message shows under 'Registration closes' for a closing time equal to the opening time, and nothing is saved.</t>
@@ -6644,7 +6654,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -6676,7 +6686,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 6: 'Registration closes at must be after it opens.' shows under 'Registration closes', and nothing is saved.
 Step 8: The same message shows under 'Registration closes' for a closing time equal to the opening time, and nothing is saved.</t>
@@ -6744,7 +6754,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 6: 'Registration closes at must be after it opens.' shows under 'Registration closes', and nothing is saved.
 Step 8: The same message shows under 'Registration closes' for a closing time equal to the opening time, and nothing is saved.</t>
@@ -7809,7 +7819,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC13</t>
         </is>
@@ -7821,7 +7831,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -7835,7 +7845,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -7854,7 +7864,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum (starts 18 Mar 2027, 09:00) | Opens: 1 Feb 2027, 09:00 | Closes: 18 Mar 2027, 09:01, then 09:00</t>
         </is>
@@ -7866,7 +7876,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 6: 'Registration must close no later than the event starts.' shows under 'Registration closes', and nothing is saved.
 Step 8: 'Registration settings saved.' appears, and the card shows 'Closes: 18 Mar 2027, 09:00'.</t>
@@ -7879,7 +7889,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -7911,7 +7921,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 6: 'Registration must close no later than the event starts.' shows under 'Registration closes', and nothing is saved.
 Step 8: 'Registration settings saved.' appears, and the card shows 'Closes: 18 Mar 2027, 09:00'.</t>
@@ -7979,7 +7989,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 6: 'Registration must close no later than the event starts.' shows under 'Registration closes', and nothing is saved.
 Step 8: 'Registration settings saved.' appears, and the card shows 'Closes: 18 Mar 2027, 09:00'.</t>
@@ -9044,7 +9054,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC14</t>
         </is>
@@ -9056,7 +9066,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -9070,7 +9080,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Closed Registration Seminar'
 2. Click 'Change registration settings' on the Registration card
@@ -9085,7 +9095,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Closed Registration Seminar (Confirmed, starts 10 Mar 2027, 09:00) | Closes: 30 Sept 2026, 17:00 (already past) -&gt; 28 Feb 2027, 17:00</t>
         </is>
@@ -9097,7 +9107,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: The card shows 'Closes: 30 Sept 2026, 17:00', a date that has already passed.
 Step 4: 'Registration settings saved.' appears. The card shows 'Opens: 1 Aug 2026, 09:00' and 'Closes: 28 Feb 2027, 17:00'. The status badge still reads 'Confirmed'.</t>
@@ -9110,7 +9120,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -9142,7 +9152,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The card shows 'Closes: 30 Sept 2026, 17:00', a date that has already passed.
 Step 4: 'Registration settings saved.' appears. The card shows 'Opens: 1 Aug 2026, 09:00' and 'Closes: 28 Feb 2027, 17:00'. The status badge still reads 'Confirmed'.</t>
@@ -9210,7 +9220,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The card shows 'Closes: 30 Sept 2026, 17:00', a date that has already passed.
 Step 4: 'Registration settings saved.' appears. The card shows 'Opens: 1 Aug 2026, 09:00' and 'Closes: 28 Feb 2027, 17:00'. The status badge still reads 'Confirmed'.</t>
@@ -10275,7 +10285,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC15</t>
         </is>
@@ -10287,7 +10297,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -10301,7 +10311,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Started Showcase'
 2. Click 'Change registration settings' on the Registration card
@@ -10317,7 +10327,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Started Showcase (Confirmed, started 1 Oct 2026, 09:00) | Closes: 1 Oct 2026, 09:00 -&gt; 2 Oct 2026, 09:00</t>
         </is>
@@ -10329,7 +10339,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'The event has started, so the registration period can't be changed.' shows under 'Registration closes', and nothing is saved.
 Step 5: The card still shows 'Closes: 1 Oct 2026, 09:00'.</t>
@@ -10342,7 +10352,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -10374,7 +10384,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'The event has started, so the registration period can't be changed.' shows under 'Registration closes', and nothing is saved.
 Step 5: The card still shows 'Closes: 1 Oct 2026, 09:00'.</t>
@@ -10442,7 +10452,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'The event has started, so the registration period can't be changed.' shows under 'Registration closes', and nothing is saved.
 Step 5: The card still shows 'Closes: 1 Oct 2026, 09:00'.</t>
@@ -11514,7 +11524,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC16</t>
         </is>
@@ -11526,7 +11536,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -11540,7 +11550,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Incomplete Setup Gala'
 2. Click 'Confirm event'
@@ -11563,7 +11573,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Incomplete Setup Gala (Planning, approved Orchard Seminar Room Classroom booking, no equipment, registration on with nothing else set) | Capacity: 60 | Opens: 1 Mar 2027, 09:00 | Closes: 27 Apr 2027, 17:00</t>
         </is>
@@ -11575,7 +11585,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows an amber alert 'Registration setup is incomplete' reading 'Still needed: registration capacity, opening date, closing date.'
 Step 2: The 'Confirm this event?' dialog opens.
@@ -11592,7 +11602,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -11624,7 +11634,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows an amber alert 'Registration setup is incomplete' reading 'Still needed: registration capacity, opening date, closing date.'
 Step 2: The 'Confirm this event?' dialog opens.
@@ -11696,7 +11706,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows an amber alert 'Registration setup is incomplete' reading 'Still needed: registration capacity, opening date, closing date.'
 Step 2: The 'Confirm this event?' dialog opens.
@@ -12774,7 +12784,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC17</t>
         </is>
@@ -12786,7 +12796,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -12800,7 +12810,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Incomplete Setup Gala'
 2. Click 'Change registration settings' on the Registration card
@@ -12817,7 +12827,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Incomplete Setup Gala (Planning, registration on with nothing else set) | Registration: on -&gt; off</t>
         </is>
@@ -12829,7 +12839,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears. The card shows 'Registration: Not enabled for this event', and the amber 'Registration setup is incomplete' alert is gone.
 Step 6: The notice 'The event is confirmed. The organiser can now see the arrangements.' appears, and the status badge reads 'Confirmed'.</t>
@@ -12842,7 +12852,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -12874,7 +12884,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears. The card shows 'Registration: Not enabled for this event', and the amber 'Registration setup is incomplete' alert is gone.
 Step 6: The notice 'The event is confirmed. The organiser can now see the arrangements.' appears, and the status badge reads 'Confirmed'.</t>
@@ -12942,7 +12952,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears. The card shows 'Registration: Not enabled for this event', and the amber 'Registration setup is incomplete' alert is gone.
 Step 6: The notice 'The event is confirmed. The organiser can now see the arrangements.' appears, and the status badge reads 'Confirmed'.</t>
@@ -14016,7 +14026,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC18</t>
         </is>
@@ -14028,7 +14038,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -14042,7 +14052,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Lost Booking Expo'
 2. Click 'Confirm event'
@@ -14058,7 +14068,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Lost Booking Expo | Capacity 40, measured against an Orchard Seminar Room booking that was rejected | Remaining booking: Orchard Studio, Classroom, up to 40 (Approved)</t>
         </is>
@@ -14070,7 +14080,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Capacity: 40' and an amber alert 'Registration setup is incomplete' reading 'The venue booking the capacity was measured against is no longer active. Choose another booking.'
 Step 3: A red alert reads 'This event cannot be confirmed yet: registration capacity is measured against a venue booking that is no longer active.' The status badge still reads 'Planning'.
@@ -14085,7 +14095,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -14117,7 +14127,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Capacity: 40' and an amber alert 'Registration setup is incomplete' reading 'The venue booking the capacity was measured against is no longer active. Choose another booking.'
 Step 3: A red alert reads 'This event cannot be confirmed yet: registration capacity is measured against a venue booking that is no longer active.' The status badge still reads 'Planning'.
@@ -14187,7 +14197,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Capacity: 40' and an amber alert 'Registration setup is incomplete' reading 'The venue booking the capacity was measured against is no longer active. Choose another booking.'
 Step 3: A red alert reads 'This event cannot be confirmed yet: registration capacity is measured against a venue booking that is no longer active.' The status badge still reads 'Planning'.
@@ -15256,7 +15266,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC01</t>
         </is>
@@ -15268,7 +15278,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -15282,7 +15292,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -15298,7 +15308,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum (Planning) | Registration: off -&gt; on</t>
         </is>
@@ -15310,7 +15320,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and a 'Change registration settings' button.
 Step 2: The card shows the checkbox 'Attendees need to register for this event', not ticked, and the buttons 'Save registration settings' and 'Cancel'.
@@ -15326,7 +15336,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -15358,7 +15368,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and a 'Change registration settings' button.
 Step 2: The card shows the checkbox 'Attendees need to register for this event', not ticked, and the buttons 'Save registration settings' and 'Cancel'.
@@ -15429,7 +15439,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and a 'Change registration settings' button.
 Step 2: The card shows the checkbox 'Attendees need to register for this event', not ticked, and the buttons 'Save registration settings' and 'Cancel'.
@@ -16497,7 +16507,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC19</t>
         </is>
@@ -16509,7 +16519,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -16523,7 +16533,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Full House Masterclass'
 2. Click 'Change registration settings' on the Registration card
@@ -16538,7 +16548,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Full House Masterclass | 12 registered, 3 waitlisted, 2 withdrawn (15 hold a place) | Capacity: 20 -&gt; 14</t>
         </is>
@@ -16550,7 +16560,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with a 'Flagged for review' list holding one line: 'Registrations: 15 attendees – the registration capacity was lowered below the number registered or waitlisted'. The card shows 'Capacity: 14'.</t>
         </is>
@@ -16562,7 +16572,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -16594,7 +16604,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with a 'Flagged for review' list holding one line: 'Registrations: 15 attendees – the registration capacity was lowered below the number registered or waitlisted'. The card shows 'Capacity: 14'.</t>
         </is>
@@ -16661,7 +16671,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with a 'Flagged for review' list holding one line: 'Registrations: 15 attendees – the registration capacity was lowered below the number registered or waitlisted'. The card shows 'Capacity: 14'.</t>
         </is>
@@ -17725,7 +17735,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC20</t>
         </is>
@@ -17737,7 +17747,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -17751,7 +17761,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Full House Masterclass'
 2. Click 'Change registration settings' on the Registration card
@@ -17766,7 +17776,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Full House Masterclass | 15 hold a place (12 registered, 3 waitlisted) | Capacity: 20 -&gt; 15</t>
         </is>
@@ -17778,7 +17788,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with no 'Flagged for review' list. The card shows 'Capacity: 15'.</t>
         </is>
@@ -17790,7 +17800,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -17822,7 +17832,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with no 'Flagged for review' list. The card shows 'Capacity: 15'.</t>
         </is>
@@ -17889,7 +17899,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with no 'Flagged for review' list. The card shows 'Capacity: 15'.</t>
         </is>
@@ -18953,7 +18963,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC21</t>
         </is>
@@ -18965,7 +18975,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -18979,7 +18989,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Waitlist Only Briefing'
 2. Click 'Change registration settings' on the Registration card
@@ -18994,7 +19004,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Waitlist Only Briefing | 0 registered, 4 waitlisted | Registration: on -&gt; off</t>
         </is>
@@ -19006,7 +19016,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with a 'Flagged for review' list holding one line: 'Registrations: 4 attendees – registration was turned off'. The card shows 'Registration: Not enabled for this event'.</t>
         </is>
@@ -19018,7 +19028,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -19050,7 +19060,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with a 'Flagged for review' list holding one line: 'Registrations: 4 attendees – registration was turned off'. The card shows 'Registration: Not enabled for this event'.</t>
         </is>
@@ -19117,7 +19127,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Registration settings saved.' appears with a 'Flagged for review' list holding one line: 'Registrations: 4 attendees – registration was turned off'. The card shows 'Registration: Not enabled for this event'.</t>
         </is>
@@ -20181,7 +20191,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC22</t>
         </is>
@@ -20193,7 +20203,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -20207,7 +20217,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Attendee Open Day'
 2. Note the event's reference (EVT- number) shown on the page
@@ -20227,7 +20237,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Attendee Open Day (Confirmed) | Lee Wei Ming: registered | Anita Devi: withdrawn | Registration: on -&gt; off</t>
         </is>
@@ -20239,7 +20249,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Registration settings saved.' appears with the 'Flagged for review' line 'Registrations: 1 attendee – registration was turned off'.
 Step 7: The 'SPM64 Attendee Open Day' event page opens with the 'Confirmed' status badge, and the Registration card reads 'Registration: Not enabled for this event'.
@@ -20253,7 +20263,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -20285,7 +20295,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Registration settings saved.' appears with the 'Flagged for review' line 'Registrations: 1 attendee – registration was turned off'.
 Step 7: The 'SPM64 Attendee Open Day' event page opens with the 'Confirmed' status badge, and the Registration card reads 'Registration: Not enabled for this event'.
@@ -20354,7 +20364,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Registration settings saved.' appears with the 'Flagged for review' line 'Registrations: 1 attendee – registration was turned off'.
 Step 7: The 'SPM64 Attendee Open Day' event page opens with the 'Confirmed' status badge, and the Registration card reads 'Registration: Not enabled for this event'.
@@ -21420,7 +21430,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC23</t>
         </is>
@@ -21432,7 +21442,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Nothing is saved in this case.
@@ -21446,7 +21456,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM64 Twin Room Workshop'
 2. Click 'My Events' in the sidebar and open 'SPM64 Closed Registration Seminar'
@@ -21461,7 +21471,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Events: SPM64 Twin Room Workshop (registration off), SPM64 Closed Registration Seminar (on, capacity 50, 1 Aug 2026 09:00 – 30 Sept 2026 17:00) | Organiser: Evelyn Chen | Colleague: Raj Kumar (Straits Medical Institute)</t>
         </is>
@@ -21473,7 +21483,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and no 'Change registration settings' button.
 Step 2: The card shows 'Registration: Enabled', 'Capacity: 50', 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00', with no 'Change registration settings' button.
@@ -21487,7 +21497,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -21519,7 +21529,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and no 'Change registration settings' button.
 Step 2: The card shows 'Registration: Enabled', 'Capacity: 50', 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00', with no 'Change registration settings' button.
@@ -21588,7 +21598,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Registration card shows 'Registration: Not enabled for this event' and no 'Change registration settings' button.
 Step 2: The card shows 'Registration: Enabled', 'Capacity: 50', 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00', with no 'Change registration settings' button.
@@ -22632,7 +22642,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.88" customWidth="1" style="19" min="1" max="1"/>
@@ -22640,33 +22650,40 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" s="19">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>SPM-64-TC24</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="111.75" customHeight="1" s="19">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-64-TC24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="233.25" customHeight="1" s="19">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Nothing is saved in this case.
@@ -22674,13 +22691,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="233.25" customHeight="1" s="19">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="71.25" customHeight="1" s="19">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Closed Registration Seminar'
 2. Log out and log in as Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager
@@ -22694,25 +22711,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="71.25" customHeight="1" s="19">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Events: SPM64 Closed Registration Seminar (Confirmed, coordinator Daniel Tan, registration on, capacity 50), SPM64 Twin Room Workshop (Planning, pending Orchard Studio booking, registration off) | Users: Priya Raj, Grace Lim, Marcus Wong, Kenji Sato</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="179.25" customHeight="1" s="19">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Events: SPM64 Closed Registration Seminar (Confirmed, coordinator Daniel Tan, registration on, capacity 50), SPM64 Twin Room Workshop (Planning, pending Orchard Studio booking, registration off) | Users: Priya Raj, Grace Lim, Marcus Wong, Kenji Sato</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="19">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page opens. The Registration card shows 'Registration: Enabled' and 'Capacity: 50', with no 'Change registration settings' button.
 Step 3: The same card, with no 'Change registration settings' button.
@@ -22722,45 +22739,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="19">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="12" customHeight="1" s="19">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="19">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="19"/>
-    <row r="10" ht="12.75" customHeight="1" s="19">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="12.75" customHeight="1" s="19"/>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1" s="19">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page opens. The Registration card shows 'Registration: Enabled' and 'Capacity: 50', with no 'Change registration settings' button.
 Step 3: The same card, with no 'Change registration settings' button.
@@ -22770,68 +22787,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="12" customHeight="1" s="19">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="12" customHeight="1" s="19">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="19">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Sammi Chua</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1" s="19">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="19"/>
-    <row r="17" ht="15.75" customHeight="1" s="19">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="19"/>
+    <row r="18" ht="15.75" customHeight="1" s="19">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page opens. The Registration card shows 'Registration: Enabled' and 'Capacity: 50', with no 'Change registration settings' button.
 Step 3: The same card, with no 'Change registration settings' button.
@@ -22841,53 +22858,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="19">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="19">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46305</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="19"/>
     <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19"/>
@@ -23866,6 +23882,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -23899,7 +23918,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC25</t>
         </is>
@@ -23911,7 +23930,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Nothing is saved in this case.
@@ -23925,7 +23944,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Attendee Open Day'
 2. Note the event's reference (EVT- number) shown on the page
@@ -23940,7 +23959,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Attendee Open Day (Confirmed, registration on, capacity 60) | Attendee: Lee Wei Ming</t>
         </is>
@@ -23952,7 +23971,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: The event page opens. The Registration card shows 'Registration: Enabled' and 'Capacity: 60', with no 'Change registration settings' button.</t>
         </is>
@@ -23964,7 +23983,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -23996,7 +24015,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: The event page opens. The Registration card shows 'Registration: Enabled' and 'Capacity: 60', with no 'Change registration settings' button.</t>
         </is>
@@ -24063,7 +24082,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: The event page opens. The Registration card shows 'Registration: Enabled' and 'Capacity: 60', with no 'Change registration settings' button.</t>
         </is>
@@ -25127,7 +25146,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC02</t>
         </is>
@@ -25139,7 +25158,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -25153,7 +25172,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Closed Registration Seminar'
 2. Click 'Change registration settings' on the Registration card
@@ -25171,7 +25190,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Closed Registration Seminar (Confirmed, no registrations) | Capacity 50 | Opens 1 Aug 2026, 09:00 | Closes 30 Sept 2026, 17:00</t>
         </is>
@@ -25183,7 +25202,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: The card shows 'Registration: Enabled', 'Capacity: 50', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00'.
 Step 4: 'Registration settings saved.' appears, the card shows 'Registration: Not enabled for this event', and no 'Flagged for review' list is shown (nobody holds a place). The status badge still reads 'Confirmed'.
@@ -25198,7 +25217,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -25230,7 +25249,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The card shows 'Registration: Enabled', 'Capacity: 50', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00'.
 Step 4: 'Registration settings saved.' appears, the card shows 'Registration: Not enabled for this event', and no 'Flagged for review' list is shown (nobody holds a place). The status badge still reads 'Confirmed'.
@@ -25300,7 +25319,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The card shows 'Registration: Enabled', 'Capacity: 50', 'Opens: 1 Aug 2026, 09:00' and 'Closes: 30 Sept 2026, 17:00'.
 Step 4: 'Registration settings saved.' appears, the card shows 'Registration: Not enabled for this event', and no 'Flagged for review' list is shown (nobody holds a place). The status badge still reads 'Confirmed'.
@@ -26367,7 +26386,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC03</t>
         </is>
@@ -26379,7 +26398,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -26393,7 +26412,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Postponed Product Talk'</t>
         </is>
@@ -26405,7 +26424,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Postponed Product Talk (Postponed, coordinator Daniel Tan)</t>
         </is>
@@ -26417,7 +26436,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: The status badge reads 'Postponed'. The Registration card shows 'Registration: Not enabled for this event' and has no 'Change registration settings' button.</t>
         </is>
@@ -26429,7 +26448,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -26461,7 +26480,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The status badge reads 'Postponed'. The Registration card shows 'Registration: Not enabled for this event' and has no 'Change registration settings' button.</t>
         </is>
@@ -26528,7 +26547,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The status badge reads 'Postponed'. The Registration card shows 'Registration: Not enabled for this event' and has no 'Change registration settings' button.</t>
         </is>
@@ -27592,7 +27611,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC04</t>
         </is>
@@ -27604,7 +27623,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -27618,7 +27637,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -27634,7 +27653,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum (one approved booking: Orchard Seminar Room, Classroom, up to 70) | Registration capacity: 60</t>
         </is>
@@ -27646,7 +27665,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' appears. There is no 'Capacity measured against' field, because the event has one booking.
 Step 5: 'Registration settings saved.' appears. The card shows 'Capacity: 60' and 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70'.</t>
@@ -27659,7 +27678,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -27691,7 +27710,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' appears. There is no 'Capacity measured against' field, because the event has one booking.
 Step 5: 'Registration settings saved.' appears. The card shows 'Capacity: 60' and 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70'.</t>
@@ -27759,7 +27778,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Registration capacity' appears. There is no 'Capacity measured against' field, because the event has one booking.
 Step 5: 'Registration settings saved.' appears. The card shows 'Capacity: 60' and 'Measured against: Orchard Seminar Room (ORC-SEM), Classroom layout – up to 70'.
@@ -28825,7 +28844,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC05</t>
         </is>
@@ -28837,7 +28856,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -28851,7 +28870,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -28872,7 +28891,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum | Registration capacity: 0, then -5, then 12.5</t>
         </is>
@@ -28884,7 +28903,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Enter a whole number, at least 1.' shows under 'Registration capacity'. The form stays open and no 'Registration settings saved.' alert appears.
 Step 7: The same message shows under 'Registration capacity', and nothing is saved.
@@ -28899,7 +28918,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -28931,7 +28950,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Enter a whole number, at least 1.' shows under 'Registration capacity'. The form stays open and no 'Registration settings saved.' alert appears.
 Step 7: The same message shows under 'Registration capacity', and nothing is saved.
@@ -29001,7 +29020,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Enter a whole number, at least 1.' shows under 'Registration capacity'. The form stays open and no 'Registration settings saved.' alert appears.
 Step 7: The same message shows under 'Registration capacity', and nothing is saved.
@@ -30068,7 +30087,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC06</t>
         </is>
@@ -30080,7 +30099,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Before and after: run `npm run fixtures:spm64` (never `npx prisma db seed`, which wipes everyone's data).
@@ -30094,7 +30113,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Orchard Data Forum'
 2. Click 'Change registration settings' on the Registration card
@@ -30112,7 +30131,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Orchard Data Forum | Booking: Orchard Seminar Room, Classroom layout (70; the room holds 120 as a theatre) | Capacity: 71, then 70</t>
         </is>
@@ -30124,7 +30143,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Registration capacity can't be more than 70, the capacity of Orchard Seminar Room (ORC-SEM) in its Classroom layout.' shows under 'Registration capacity', and nothing is saved. The room's 120-seat theatre capacity is not used.
 Step 7: 'Registration settings saved.' appears, and the card shows 'Capacity: 70'.</t>
@@ -30137,7 +30156,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -30169,7 +30188,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Registration capacity can't be more than 70, the capacity of Orchard Seminar Room (ORC-SEM) in its Classroom layout.' shows under 'Registration capacity', and nothing is saved. The room's 120-seat theatre capacity is not used.
 Step 7: 'Registration settings saved.' appears, and the card shows 'Capacity: 70'.</t>
@@ -30237,7 +30256,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Registration capacity can't be more than 70, the capacity of Orchard Seminar Room (ORC-SEM) in its Classroom layout.' shows under 'Registration capacity', and nothing is saved. The room's 120-seat theatre capacity is not used.
 Step 7: 'Registration settings saved.' appears, and the card shows 'Capacity: 70'.</t>
@@ -31302,7 +31321,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC07</t>
         </is>
@@ -31314,7 +31333,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -31328,7 +31347,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Unbooked Strategy Day'
 2. Click 'Change registration settings' on the Registration card
@@ -31344,7 +31363,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Unbooked Strategy Day (Approved, no venue bookings) | Capacity: 30</t>
         </is>
@@ -31356,7 +31375,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Book a venue for this event before setting a registration capacity.' shows under 'Registration capacity'. The form stays open and nothing is saved.</t>
         </is>
@@ -31368,7 +31387,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -31400,7 +31419,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Book a venue for this event before setting a registration capacity.' shows under 'Registration capacity'. The form stays open and nothing is saved.</t>
         </is>
@@ -31467,7 +31486,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'Book a venue for this event before setting a registration capacity.' shows under 'Registration capacity'. The form stays open and nothing is saved.</t>
         </is>
@@ -32531,7 +32550,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-64-TC08</t>
         </is>
@@ -32543,7 +32562,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm64` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM64 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -32557,7 +32576,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM64 Layout-Free Networking Night'
 2. Click 'Change registration settings' on the Registration card
@@ -32573,7 +32592,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM64 Layout-Free Networking Night (approved booking at Orchard Seminar Room with no layout) | Capacity: 30</t>
         </is>
@@ -32585,7 +32604,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'The venue booking has no room layout, so its capacity isn't known. Book the venue with a room layout first.' shows under 'Registration capacity'. The form stays open and nothing is saved.</t>
         </is>
@@ -32597,7 +32616,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -32629,7 +32648,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'The venue booking has no room layout, so its capacity isn't known. Book the venue with a room layout first.' shows under 'Registration capacity'. The form stays open and nothing is saved.</t>
         </is>
@@ -32696,7 +32715,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 5: 'The venue booking has no room layout, so its capacity isn't known. Book the venue with a room layout first.' shows under 'Registration capacity'. The form stays open and nothing is saved.</t>
         </is>
